--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-la-araucania.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-la-araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>765-174-CM26</t>
+          <t>1175-133-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,494 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>50825.13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1175-147-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.083.021-6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>41533.23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2546-20-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SolNet SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>26330.16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>765-316-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MICROSYSTEM S.A.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>94.099.000-9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>132651.46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>765-349-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>10590.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>986278-204-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>65.148.017-5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>6702.97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>722-158-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>72.201.100-7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.083.021-6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>25422.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>765-406-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.083.021-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>14785.64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>765-174-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RIALIS SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.348.639-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>31171.73</v>
       </c>
     </row>
